--- a/ci-cd-merge-resolver/repoCollector/datasets/atmosphere.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/atmosphere.xlsx
@@ -150,16 +150,16 @@
         <v>1.0</v>
       </c>
       <c r="G2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>43.52000045776367</v>
+        <v>36.52000045776367</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
